--- a/MeasureControl/加放油测试脚本V3.xlsx
+++ b/MeasureControl/加放油测试脚本V3.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\software\VisualStudio\Project\MC_Beta\MeasureControl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\application\C#\project\20260424\MeasureControl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C672322-FAE6-44B5-B6F3-ACA81AA75310}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5862D612-4297-4A58-A438-8A35B03B5D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -677,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -715,18 +715,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -751,15 +745,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -772,24 +781,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -799,23 +790,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1106,7 +1088,7 @@
   <dimension ref="A1:N58"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="20.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.375" style="16" customWidth="1"/>
+    <col min="1" max="1" width="19.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="42.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="82.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="32.875" style="2" customWidth="1"/>
@@ -1120,20 +1102,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="69.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1174,13 +1156,13 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1204,13 +1186,13 @@
       <c r="J3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K3" s="23"/>
-      <c r="L3" s="41"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="38"/>
     </row>
     <row r="4" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
       <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
@@ -1232,13 +1214,13 @@
       <c r="J4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="23"/>
-      <c r="L4" s="42"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="38"/>
     </row>
     <row r="5" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
       <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
@@ -1260,13 +1242,13 @@
       <c r="J5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="42"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="38"/>
     </row>
     <row r="6" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
@@ -1288,8 +1270,8 @@
       <c r="J6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K6" s="21"/>
-      <c r="L6" s="43"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="38"/>
     </row>
     <row r="7" spans="1:14" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
@@ -1316,15 +1298,15 @@
       <c r="H7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="18">
         <v>18</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="13"/>
-      <c r="N7" s="14"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="20"/>
+      <c r="N7" s="13"/>
     </row>
     <row r="8" spans="1:14" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
@@ -1336,7 +1318,7 @@
       <c r="C8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -1357,8 +1339,8 @@
       <c r="J8" s="10">
         <v>15</v>
       </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="22"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="20"/>
     </row>
     <row r="9" spans="1:14" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -1385,32 +1367,32 @@
       <c r="H9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="18">
         <v>18</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="J9" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="22"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="20"/>
     </row>
     <row r="10" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="27" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="27" t="s">
         <v>75</v>
       </c>
       <c r="G10" s="7" t="s">
@@ -1419,628 +1401,628 @@
       <c r="H10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="35">
         <v>18</v>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="18">
         <v>1</v>
       </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="44"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="36"/>
+      <c r="F11" s="29"/>
       <c r="G11" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="17">
+      <c r="I11" s="36"/>
+      <c r="J11" s="15">
         <v>1</v>
       </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="45"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="40"/>
     </row>
     <row r="12" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
       <c r="E12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="36"/>
+      <c r="F12" s="29"/>
       <c r="G12" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="39"/>
-      <c r="J12" s="20">
+      <c r="I12" s="36"/>
+      <c r="J12" s="18">
         <v>1</v>
       </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="45"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="40"/>
     </row>
     <row r="13" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
       <c r="E13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="36"/>
+      <c r="F13" s="29"/>
       <c r="G13" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="39"/>
-      <c r="J13" s="20">
+      <c r="I13" s="36"/>
+      <c r="J13" s="18">
         <v>1</v>
       </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="45"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="40"/>
     </row>
     <row r="14" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="36"/>
+      <c r="F14" s="29"/>
       <c r="G14" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="39"/>
-      <c r="J14" s="17">
+      <c r="I14" s="36"/>
+      <c r="J14" s="15">
         <v>1</v>
       </c>
-      <c r="K14" s="19"/>
-      <c r="L14" s="45"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="40"/>
     </row>
     <row r="15" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="36"/>
+      <c r="F15" s="29"/>
       <c r="G15" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="39"/>
-      <c r="J15" s="20">
+      <c r="I15" s="36"/>
+      <c r="J15" s="18">
         <v>1</v>
       </c>
-      <c r="K15" s="19"/>
-      <c r="L15" s="45"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="40"/>
     </row>
     <row r="16" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="36"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
       <c r="E16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="36"/>
+      <c r="F16" s="29"/>
       <c r="G16" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="20">
+      <c r="I16" s="36"/>
+      <c r="J16" s="18">
         <v>1</v>
       </c>
-      <c r="K16" s="19"/>
-      <c r="L16" s="45"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="40"/>
     </row>
     <row r="17" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
       <c r="E17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="36"/>
+      <c r="F17" s="29"/>
       <c r="G17" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="39"/>
-      <c r="J17" s="17">
+      <c r="I17" s="36"/>
+      <c r="J17" s="15">
         <v>1</v>
       </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="45"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="40"/>
     </row>
     <row r="18" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
       <c r="E18" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="36"/>
+      <c r="F18" s="29"/>
       <c r="G18" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="39"/>
-      <c r="J18" s="20">
+      <c r="I18" s="36"/>
+      <c r="J18" s="18">
         <v>1</v>
       </c>
-      <c r="K18" s="19"/>
-      <c r="L18" s="45"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="40"/>
     </row>
     <row r="19" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
       <c r="E19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="36"/>
+      <c r="F19" s="29"/>
       <c r="G19" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I19" s="39"/>
-      <c r="J19" s="20">
+      <c r="I19" s="36"/>
+      <c r="J19" s="18">
         <v>1</v>
       </c>
-      <c r="K19" s="19"/>
-      <c r="L19" s="45"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="40"/>
     </row>
     <row r="20" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
       <c r="E20" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="36"/>
+      <c r="F20" s="29"/>
       <c r="G20" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="20">
+      <c r="I20" s="36"/>
+      <c r="J20" s="18">
         <v>1</v>
       </c>
-      <c r="K20" s="19"/>
-      <c r="L20" s="45"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="40"/>
     </row>
     <row r="21" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
       <c r="E21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="36"/>
+      <c r="F21" s="29"/>
       <c r="G21" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I21" s="39"/>
-      <c r="J21" s="20">
+      <c r="I21" s="36"/>
+      <c r="J21" s="18">
         <v>1</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="45"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="40"/>
     </row>
     <row r="22" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
       <c r="E22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="36"/>
+      <c r="F22" s="29"/>
       <c r="G22" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="20">
+      <c r="I22" s="36"/>
+      <c r="J22" s="18">
         <v>1</v>
       </c>
-      <c r="K22" s="19"/>
-      <c r="L22" s="45"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="40"/>
     </row>
     <row r="23" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="36"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="29"/>
       <c r="E23" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="36"/>
+      <c r="F23" s="29"/>
       <c r="G23" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="20">
+      <c r="I23" s="36"/>
+      <c r="J23" s="18">
         <v>1</v>
       </c>
-      <c r="K23" s="19"/>
-      <c r="L23" s="45"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="40"/>
     </row>
     <row r="24" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="35" t="s">
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="36"/>
+      <c r="D24" s="29"/>
       <c r="E24" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="36"/>
+      <c r="F24" s="29"/>
       <c r="G24" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="20">
+      <c r="I24" s="36"/>
+      <c r="J24" s="18">
         <v>0</v>
       </c>
-      <c r="K24" s="19"/>
-      <c r="L24" s="45"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="40"/>
     </row>
     <row r="25" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
       <c r="E25" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="36"/>
+      <c r="F25" s="29"/>
       <c r="G25" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="20">
+      <c r="I25" s="36"/>
+      <c r="J25" s="18">
         <v>0</v>
       </c>
-      <c r="K25" s="19"/>
-      <c r="L25" s="45"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="40"/>
     </row>
     <row r="26" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
       <c r="E26" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="36"/>
+      <c r="F26" s="29"/>
       <c r="G26" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="20">
+      <c r="I26" s="36"/>
+      <c r="J26" s="18">
         <v>0</v>
       </c>
-      <c r="K26" s="19"/>
-      <c r="L26" s="45"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="40"/>
     </row>
     <row r="27" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
       <c r="E27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="36"/>
+      <c r="F27" s="29"/>
       <c r="G27" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I27" s="39"/>
-      <c r="J27" s="20">
+      <c r="I27" s="36"/>
+      <c r="J27" s="18">
         <v>0</v>
       </c>
-      <c r="K27" s="19"/>
-      <c r="L27" s="45"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="40"/>
     </row>
     <row r="28" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
       <c r="E28" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F28" s="36"/>
+      <c r="F28" s="29"/>
       <c r="G28" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I28" s="39"/>
+      <c r="I28" s="36"/>
       <c r="J28" s="12">
         <v>0</v>
       </c>
-      <c r="K28" s="19"/>
-      <c r="L28" s="45"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="40"/>
     </row>
     <row r="29" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
       <c r="E29" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="36"/>
+      <c r="F29" s="29"/>
       <c r="G29" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I29" s="39"/>
-      <c r="J29" s="20">
+      <c r="I29" s="36"/>
+      <c r="J29" s="18">
         <v>0</v>
       </c>
-      <c r="K29" s="19"/>
-      <c r="L29" s="45"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="40"/>
     </row>
     <row r="30" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
       <c r="E30" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="36"/>
+      <c r="F30" s="29"/>
       <c r="G30" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I30" s="39"/>
-      <c r="J30" s="20">
+      <c r="I30" s="36"/>
+      <c r="J30" s="18">
         <v>0</v>
       </c>
-      <c r="K30" s="19"/>
-      <c r="L30" s="45"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="40"/>
     </row>
     <row r="31" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
       <c r="E31" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="36"/>
+      <c r="F31" s="29"/>
       <c r="G31" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I31" s="39"/>
-      <c r="J31" s="20">
+      <c r="I31" s="36"/>
+      <c r="J31" s="18">
         <v>0</v>
       </c>
-      <c r="K31" s="19"/>
-      <c r="L31" s="45"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="40"/>
     </row>
     <row r="32" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
       <c r="E32" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="36"/>
+      <c r="F32" s="29"/>
       <c r="G32" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I32" s="39"/>
-      <c r="J32" s="20">
+      <c r="I32" s="36"/>
+      <c r="J32" s="18">
         <v>0</v>
       </c>
-      <c r="K32" s="19"/>
-      <c r="L32" s="45"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="40"/>
     </row>
     <row r="33" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
       <c r="E33" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="36"/>
+      <c r="F33" s="29"/>
       <c r="G33" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I33" s="39"/>
-      <c r="J33" s="20">
+      <c r="I33" s="36"/>
+      <c r="J33" s="18">
         <v>0</v>
       </c>
-      <c r="K33" s="19"/>
-      <c r="L33" s="45"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="40"/>
     </row>
     <row r="34" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
       <c r="E34" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="36"/>
+      <c r="F34" s="29"/>
       <c r="G34" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I34" s="39"/>
-      <c r="J34" s="20">
+      <c r="I34" s="36"/>
+      <c r="J34" s="18">
         <v>0</v>
       </c>
-      <c r="K34" s="19"/>
-      <c r="L34" s="45"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="40"/>
     </row>
     <row r="35" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F35" s="36"/>
+      <c r="F35" s="29"/>
       <c r="G35" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="39"/>
-      <c r="J35" s="20">
+      <c r="I35" s="36"/>
+      <c r="J35" s="18">
         <v>0</v>
       </c>
-      <c r="K35" s="19"/>
-      <c r="L35" s="45"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="40"/>
     </row>
     <row r="36" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
       <c r="E36" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F36" s="36"/>
+      <c r="F36" s="29"/>
       <c r="G36" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I36" s="39"/>
-      <c r="J36" s="20">
+      <c r="I36" s="36"/>
+      <c r="J36" s="18">
         <v>0</v>
       </c>
-      <c r="K36" s="19"/>
-      <c r="L36" s="45"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="40"/>
     </row>
     <row r="37" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="37"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
       <c r="E37" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="37"/>
+      <c r="F37" s="28"/>
       <c r="G37" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="40"/>
-      <c r="J37" s="20">
+      <c r="I37" s="37"/>
+      <c r="J37" s="18">
         <v>0</v>
       </c>
-      <c r="K37" s="19"/>
-      <c r="L37" s="46"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="40"/>
     </row>
     <row r="38" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="35" t="s">
+      <c r="A38" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="35" t="s">
+      <c r="B38" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="32" t="s">
         <v>101</v>
       </c>
       <c r="G38" s="7" t="s">
@@ -2049,160 +2031,160 @@
       <c r="H38" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I38" s="29" t="s">
+      <c r="I38" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="J38" s="25">
+      <c r="J38" s="10">
         <v>10</v>
       </c>
-      <c r="K38" s="19"/>
-      <c r="L38" s="44"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="40"/>
     </row>
     <row r="39" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="36"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="18" t="s">
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F39" s="30"/>
+      <c r="F39" s="33"/>
       <c r="G39" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I39" s="30"/>
-      <c r="J39" s="25">
+      <c r="I39" s="33"/>
+      <c r="J39" s="10">
         <v>10</v>
       </c>
-      <c r="K39" s="19"/>
-      <c r="L39" s="45"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="40"/>
     </row>
     <row r="40" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="18" t="s">
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="F40" s="30"/>
+      <c r="F40" s="33"/>
       <c r="G40" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I40" s="30"/>
-      <c r="J40" s="25">
+      <c r="I40" s="33"/>
+      <c r="J40" s="10">
         <v>10</v>
       </c>
-      <c r="K40" s="19"/>
-      <c r="L40" s="45"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="40"/>
     </row>
     <row r="41" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="18" t="s">
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F41" s="30"/>
+      <c r="F41" s="33"/>
       <c r="G41" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I41" s="30"/>
-      <c r="J41" s="25">
+      <c r="I41" s="33"/>
+      <c r="J41" s="10">
         <v>10</v>
       </c>
-      <c r="K41" s="19"/>
-      <c r="L41" s="45"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="40"/>
     </row>
     <row r="42" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="36"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="18" t="s">
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F42" s="30"/>
+      <c r="F42" s="33"/>
       <c r="G42" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I42" s="30"/>
-      <c r="J42" s="25">
+      <c r="I42" s="33"/>
+      <c r="J42" s="10">
         <v>10</v>
       </c>
-      <c r="K42" s="19"/>
-      <c r="L42" s="45"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="36"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="18" t="s">
+      <c r="A43" s="29"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F43" s="30"/>
+      <c r="F43" s="33"/>
       <c r="G43" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I43" s="30"/>
-      <c r="J43" s="25">
+      <c r="I43" s="33"/>
+      <c r="J43" s="10">
         <v>10</v>
       </c>
-      <c r="K43" s="19"/>
-      <c r="L43" s="45"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="40"/>
     </row>
     <row r="44" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="36"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="18" t="s">
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="F44" s="31"/>
+      <c r="F44" s="34"/>
       <c r="G44" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I44" s="31"/>
-      <c r="J44" s="25">
+      <c r="I44" s="34"/>
+      <c r="J44" s="10">
         <v>10</v>
       </c>
-      <c r="K44" s="19"/>
-      <c r="L44" s="45"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="40"/>
     </row>
     <row r="45" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="35" t="s">
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D45" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F45" s="29" t="s">
+      <c r="F45" s="32" t="s">
         <v>101</v>
       </c>
       <c r="G45" s="7" t="s">
@@ -2211,157 +2193,157 @@
       <c r="H45" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I45" s="29" t="s">
+      <c r="I45" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="J45" s="25">
+      <c r="J45" s="10">
         <v>100000</v>
       </c>
-      <c r="K45" s="19"/>
-      <c r="L45" s="45"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="40"/>
     </row>
     <row r="46" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="36"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="18" t="s">
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F46" s="30"/>
+      <c r="F46" s="33"/>
       <c r="G46" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I46" s="30"/>
-      <c r="J46" s="25">
+      <c r="I46" s="33"/>
+      <c r="J46" s="10">
         <v>100000</v>
       </c>
-      <c r="K46" s="19"/>
-      <c r="L46" s="45"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="40"/>
     </row>
     <row r="47" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="36"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="18" t="s">
+      <c r="A47" s="29"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="30"/>
+      <c r="F47" s="33"/>
       <c r="G47" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I47" s="30"/>
-      <c r="J47" s="25">
+      <c r="I47" s="33"/>
+      <c r="J47" s="10">
         <v>100000</v>
       </c>
-      <c r="K47" s="19"/>
-      <c r="L47" s="45"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="40"/>
     </row>
     <row r="48" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="18" t="s">
+      <c r="A48" s="29"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F48" s="30"/>
+      <c r="F48" s="33"/>
       <c r="G48" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I48" s="30"/>
-      <c r="J48" s="25">
+      <c r="I48" s="33"/>
+      <c r="J48" s="10">
         <v>100000</v>
       </c>
-      <c r="K48" s="19"/>
-      <c r="L48" s="45"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="40"/>
     </row>
     <row r="49" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="18" t="s">
+      <c r="A49" s="29"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F49" s="30"/>
+      <c r="F49" s="33"/>
       <c r="G49" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I49" s="30"/>
-      <c r="J49" s="25">
+      <c r="I49" s="33"/>
+      <c r="J49" s="10">
         <v>100000</v>
       </c>
-      <c r="K49" s="19"/>
-      <c r="L49" s="45"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="40"/>
     </row>
     <row r="50" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="36"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="18" t="s">
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F50" s="30"/>
+      <c r="F50" s="33"/>
       <c r="G50" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I50" s="30"/>
-      <c r="J50" s="25">
+      <c r="I50" s="33"/>
+      <c r="J50" s="10">
         <v>100000</v>
       </c>
-      <c r="K50" s="19"/>
-      <c r="L50" s="45"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="40"/>
     </row>
     <row r="51" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="36"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="18" t="s">
+      <c r="A51" s="29"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="F51" s="31"/>
+      <c r="F51" s="34"/>
       <c r="G51" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H51" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I51" s="31"/>
-      <c r="J51" s="25">
+      <c r="I51" s="34"/>
+      <c r="J51" s="10">
         <v>100000</v>
       </c>
-      <c r="K51" s="19"/>
-      <c r="L51" s="45"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="40"/>
     </row>
     <row r="52" spans="1:12" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="37"/>
-      <c r="B52" s="37"/>
-      <c r="C52" s="27" t="s">
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="D52" s="24" t="s">
+      <c r="D52" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="E52" s="18" t="s">
+      <c r="E52" s="16" t="s">
         <v>30</v>
       </c>
       <c r="F52" s="10" t="s">
@@ -2373,20 +2355,20 @@
       <c r="H52" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I52" s="20">
+      <c r="I52" s="18">
         <v>18</v>
       </c>
-      <c r="J52" s="20">
+      <c r="J52" s="18">
         <v>16</v>
       </c>
-      <c r="K52" s="19"/>
-      <c r="L52" s="46"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="40"/>
     </row>
     <row r="53" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="35" t="s">
+      <c r="A53" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="25" t="s">
         <v>93</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -2410,15 +2392,15 @@
       <c r="I53" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J53" s="20" t="s">
+      <c r="J53" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="K53" s="19"/>
-      <c r="L53" s="44"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="40"/>
     </row>
     <row r="54" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="36"/>
-      <c r="B54" s="33"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="30"/>
       <c r="C54" s="10" t="s">
         <v>96</v>
       </c>
@@ -2440,15 +2422,15 @@
       <c r="I54" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J54" s="20" t="s">
+      <c r="J54" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="K54" s="19"/>
-      <c r="L54" s="45"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="39"/>
     </row>
     <row r="55" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="36"/>
-      <c r="B55" s="33"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="10" t="s">
         <v>97</v>
       </c>
@@ -2470,15 +2452,15 @@
       <c r="I55" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J55" s="20" t="s">
+      <c r="J55" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="K55" s="19"/>
-      <c r="L55" s="45"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="40"/>
     </row>
     <row r="56" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="37"/>
-      <c r="B56" s="34"/>
+      <c r="A56" s="28"/>
+      <c r="B56" s="26"/>
       <c r="C56" s="10" t="s">
         <v>94</v>
       </c>
@@ -2500,20 +2482,20 @@
       <c r="I56" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J56" s="20" t="s">
+      <c r="J56" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="K56" s="19"/>
-      <c r="L56" s="46"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="40"/>
     </row>
     <row r="57" spans="1:12" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B57" s="32" t="s">
+      <c r="B57" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="35" t="s">
+      <c r="C57" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D57" s="10" t="s">
@@ -2537,14 +2519,14 @@
       <c r="J57" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="K57" s="19"/>
-      <c r="L57" s="44"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="40"/>
     </row>
     <row r="58" spans="1:12" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="37"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="26" t="s">
+      <c r="A58" s="28"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="23" t="s">
         <v>47</v>
       </c>
       <c r="E58" s="6" t="s">
@@ -2565,26 +2547,12 @@
       <c r="J58" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="K58" s="19"/>
-      <c r="L58" s="46"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A38:A52"/>
-    <mergeCell ref="B38:B52"/>
-    <mergeCell ref="C38:C44"/>
-    <mergeCell ref="A10:A37"/>
-    <mergeCell ref="B10:B37"/>
-    <mergeCell ref="D10:D37"/>
-    <mergeCell ref="B53:B56"/>
-    <mergeCell ref="A53:A56"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C10:C23"/>
-    <mergeCell ref="L53:L56"/>
-    <mergeCell ref="L57:L58"/>
-    <mergeCell ref="L38:L52"/>
+  <mergeCells count="26">
+    <mergeCell ref="F10:F37"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="D38:D44"/>
     <mergeCell ref="D45:D51"/>
@@ -2598,9 +2566,18 @@
     <mergeCell ref="C24:C37"/>
     <mergeCell ref="C45:C51"/>
     <mergeCell ref="I10:I37"/>
-    <mergeCell ref="F10:F37"/>
-    <mergeCell ref="L3:L6"/>
-    <mergeCell ref="L10:L37"/>
+    <mergeCell ref="A10:A37"/>
+    <mergeCell ref="B10:B37"/>
+    <mergeCell ref="D10:D37"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="C10:C23"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A38:A52"/>
+    <mergeCell ref="B38:B52"/>
+    <mergeCell ref="C38:C44"/>
+    <mergeCell ref="C57:C58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MeasureControl/加放油测试脚本V3.xlsx
+++ b/MeasureControl/加放油测试脚本V3.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\application\C#\project\20260424\MeasureControl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\application\C#\project\jiaoben\MeasureControl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{5862D612-4297-4A58-A438-8A35B03B5D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -751,45 +751,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -798,6 +759,45 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1156,13 +1156,13 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1187,10 +1187,10 @@
         <v>70</v>
       </c>
       <c r="K3" s="21"/>
-      <c r="L3" s="38"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
+      <c r="A4" s="36"/>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="5" t="s">
@@ -1215,10 +1215,10 @@
         <v>70</v>
       </c>
       <c r="K4" s="21"/>
-      <c r="L4" s="38"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
       <c r="D5" s="5" t="s">
@@ -1243,12 +1243,12 @@
         <v>70</v>
       </c>
       <c r="K5" s="21"/>
-      <c r="L5" s="38"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
       <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>70</v>
       </c>
       <c r="K6" s="19"/>
-      <c r="L6" s="38"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:14" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
@@ -1377,22 +1377,22 @@
       <c r="L9" s="20"/>
     </row>
     <row r="10" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="28" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G10" s="7" t="s">
@@ -1401,14 +1401,14 @@
       <c r="H10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="38">
         <v>18</v>
       </c>
       <c r="J10" s="18">
         <v>1</v>
       </c>
       <c r="K10" s="17"/>
-      <c r="L10" s="40"/>
+      <c r="L10" s="27"/>
     </row>
     <row r="11" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29"/>
@@ -1425,12 +1425,12 @@
       <c r="H11" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I11" s="36"/>
+      <c r="I11" s="39"/>
       <c r="J11" s="15">
         <v>1</v>
       </c>
       <c r="K11" s="17"/>
-      <c r="L11" s="40"/>
+      <c r="L11" s="27"/>
     </row>
     <row r="12" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="29"/>
@@ -1447,12 +1447,12 @@
       <c r="H12" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="36"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="18">
         <v>1</v>
       </c>
       <c r="K12" s="17"/>
-      <c r="L12" s="40"/>
+      <c r="L12" s="27"/>
     </row>
     <row r="13" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29"/>
@@ -1469,12 +1469,12 @@
       <c r="H13" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="36"/>
+      <c r="I13" s="39"/>
       <c r="J13" s="18">
         <v>1</v>
       </c>
       <c r="K13" s="17"/>
-      <c r="L13" s="40"/>
+      <c r="L13" s="27"/>
     </row>
     <row r="14" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29"/>
@@ -1491,12 +1491,12 @@
       <c r="H14" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="36"/>
+      <c r="I14" s="39"/>
       <c r="J14" s="15">
         <v>1</v>
       </c>
       <c r="K14" s="17"/>
-      <c r="L14" s="40"/>
+      <c r="L14" s="27"/>
     </row>
     <row r="15" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29"/>
@@ -1513,12 +1513,12 @@
       <c r="H15" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="36"/>
+      <c r="I15" s="39"/>
       <c r="J15" s="18">
         <v>1</v>
       </c>
       <c r="K15" s="17"/>
-      <c r="L15" s="40"/>
+      <c r="L15" s="27"/>
     </row>
     <row r="16" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29"/>
@@ -1535,12 +1535,12 @@
       <c r="H16" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I16" s="36"/>
+      <c r="I16" s="39"/>
       <c r="J16" s="18">
         <v>1</v>
       </c>
       <c r="K16" s="17"/>
-      <c r="L16" s="40"/>
+      <c r="L16" s="27"/>
     </row>
     <row r="17" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29"/>
@@ -1557,12 +1557,12 @@
       <c r="H17" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="36"/>
+      <c r="I17" s="39"/>
       <c r="J17" s="15">
         <v>1</v>
       </c>
       <c r="K17" s="17"/>
-      <c r="L17" s="40"/>
+      <c r="L17" s="27"/>
     </row>
     <row r="18" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="29"/>
@@ -1579,12 +1579,12 @@
       <c r="H18" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="36"/>
+      <c r="I18" s="39"/>
       <c r="J18" s="18">
         <v>1</v>
       </c>
       <c r="K18" s="17"/>
-      <c r="L18" s="40"/>
+      <c r="L18" s="27"/>
     </row>
     <row r="19" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="29"/>
@@ -1601,12 +1601,12 @@
       <c r="H19" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I19" s="36"/>
+      <c r="I19" s="39"/>
       <c r="J19" s="18">
         <v>1</v>
       </c>
       <c r="K19" s="17"/>
-      <c r="L19" s="40"/>
+      <c r="L19" s="27"/>
     </row>
     <row r="20" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="29"/>
@@ -1623,12 +1623,12 @@
       <c r="H20" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I20" s="36"/>
+      <c r="I20" s="39"/>
       <c r="J20" s="18">
         <v>1</v>
       </c>
       <c r="K20" s="17"/>
-      <c r="L20" s="40"/>
+      <c r="L20" s="27"/>
     </row>
     <row r="21" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
@@ -1645,12 +1645,12 @@
       <c r="H21" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I21" s="36"/>
+      <c r="I21" s="39"/>
       <c r="J21" s="18">
         <v>1</v>
       </c>
       <c r="K21" s="17"/>
-      <c r="L21" s="40"/>
+      <c r="L21" s="27"/>
     </row>
     <row r="22" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="29"/>
@@ -1667,17 +1667,17 @@
       <c r="H22" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="36"/>
+      <c r="I22" s="39"/>
       <c r="J22" s="18">
         <v>1</v>
       </c>
       <c r="K22" s="17"/>
-      <c r="L22" s="40"/>
+      <c r="L22" s="27"/>
     </row>
     <row r="23" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="29"/>
       <c r="B23" s="29"/>
-      <c r="C23" s="28"/>
+      <c r="C23" s="30"/>
       <c r="D23" s="29"/>
       <c r="E23" s="5" t="s">
         <v>67</v>
@@ -1689,17 +1689,17 @@
       <c r="H23" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="36"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="18">
         <v>1</v>
       </c>
       <c r="K23" s="17"/>
-      <c r="L23" s="40"/>
+      <c r="L23" s="27"/>
     </row>
     <row r="24" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="29"/>
       <c r="B24" s="29"/>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="28" t="s">
         <v>69</v>
       </c>
       <c r="D24" s="29"/>
@@ -1713,12 +1713,12 @@
       <c r="H24" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I24" s="36"/>
+      <c r="I24" s="39"/>
       <c r="J24" s="18">
         <v>0</v>
       </c>
       <c r="K24" s="17"/>
-      <c r="L24" s="40"/>
+      <c r="L24" s="27"/>
     </row>
     <row r="25" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="29"/>
@@ -1735,12 +1735,12 @@
       <c r="H25" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="36"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="18">
         <v>0</v>
       </c>
       <c r="K25" s="17"/>
-      <c r="L25" s="40"/>
+      <c r="L25" s="27"/>
     </row>
     <row r="26" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="29"/>
@@ -1757,12 +1757,12 @@
       <c r="H26" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="36"/>
+      <c r="I26" s="39"/>
       <c r="J26" s="18">
         <v>0</v>
       </c>
       <c r="K26" s="17"/>
-      <c r="L26" s="40"/>
+      <c r="L26" s="27"/>
     </row>
     <row r="27" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="29"/>
@@ -1779,12 +1779,12 @@
       <c r="H27" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I27" s="36"/>
+      <c r="I27" s="39"/>
       <c r="J27" s="18">
         <v>0</v>
       </c>
       <c r="K27" s="17"/>
-      <c r="L27" s="40"/>
+      <c r="L27" s="27"/>
     </row>
     <row r="28" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="29"/>
@@ -1801,12 +1801,12 @@
       <c r="H28" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I28" s="36"/>
+      <c r="I28" s="39"/>
       <c r="J28" s="12">
         <v>0</v>
       </c>
       <c r="K28" s="17"/>
-      <c r="L28" s="40"/>
+      <c r="L28" s="27"/>
     </row>
     <row r="29" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29"/>
@@ -1823,12 +1823,12 @@
       <c r="H29" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I29" s="36"/>
+      <c r="I29" s="39"/>
       <c r="J29" s="18">
         <v>0</v>
       </c>
       <c r="K29" s="17"/>
-      <c r="L29" s="40"/>
+      <c r="L29" s="27"/>
     </row>
     <row r="30" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29"/>
@@ -1845,12 +1845,12 @@
       <c r="H30" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I30" s="36"/>
+      <c r="I30" s="39"/>
       <c r="J30" s="18">
         <v>0</v>
       </c>
       <c r="K30" s="17"/>
-      <c r="L30" s="40"/>
+      <c r="L30" s="27"/>
     </row>
     <row r="31" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29"/>
@@ -1867,12 +1867,12 @@
       <c r="H31" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I31" s="36"/>
+      <c r="I31" s="39"/>
       <c r="J31" s="18">
         <v>0</v>
       </c>
       <c r="K31" s="17"/>
-      <c r="L31" s="40"/>
+      <c r="L31" s="27"/>
     </row>
     <row r="32" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29"/>
@@ -1889,12 +1889,12 @@
       <c r="H32" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I32" s="36"/>
+      <c r="I32" s="39"/>
       <c r="J32" s="18">
         <v>0</v>
       </c>
       <c r="K32" s="17"/>
-      <c r="L32" s="40"/>
+      <c r="L32" s="27"/>
     </row>
     <row r="33" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
@@ -1911,12 +1911,12 @@
       <c r="H33" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I33" s="36"/>
+      <c r="I33" s="39"/>
       <c r="J33" s="18">
         <v>0</v>
       </c>
       <c r="K33" s="17"/>
-      <c r="L33" s="40"/>
+      <c r="L33" s="27"/>
     </row>
     <row r="34" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29"/>
@@ -1933,12 +1933,12 @@
       <c r="H34" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I34" s="36"/>
+      <c r="I34" s="39"/>
       <c r="J34" s="18">
         <v>0</v>
       </c>
       <c r="K34" s="17"/>
-      <c r="L34" s="40"/>
+      <c r="L34" s="27"/>
     </row>
     <row r="35" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29"/>
@@ -1955,12 +1955,12 @@
       <c r="H35" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="36"/>
+      <c r="I35" s="39"/>
       <c r="J35" s="18">
         <v>0</v>
       </c>
       <c r="K35" s="17"/>
-      <c r="L35" s="40"/>
+      <c r="L35" s="27"/>
     </row>
     <row r="36" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="29"/>
@@ -1977,43 +1977,43 @@
       <c r="H36" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I36" s="36"/>
+      <c r="I36" s="39"/>
       <c r="J36" s="18">
         <v>0</v>
       </c>
       <c r="K36" s="17"/>
-      <c r="L36" s="40"/>
+      <c r="L36" s="27"/>
     </row>
     <row r="37" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="28"/>
+      <c r="F37" s="30"/>
       <c r="G37" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="37"/>
+      <c r="I37" s="40"/>
       <c r="J37" s="18">
         <v>0</v>
       </c>
       <c r="K37" s="17"/>
-      <c r="L37" s="40"/>
+      <c r="L37" s="27"/>
     </row>
     <row r="38" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="28" t="s">
         <v>82</v>
       </c>
       <c r="D38" s="32" t="s">
@@ -2038,7 +2038,7 @@
         <v>10</v>
       </c>
       <c r="K38" s="17"/>
-      <c r="L38" s="40"/>
+      <c r="L38" s="27"/>
     </row>
     <row r="39" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="29"/>
@@ -2060,7 +2060,7 @@
         <v>10</v>
       </c>
       <c r="K39" s="17"/>
-      <c r="L39" s="40"/>
+      <c r="L39" s="27"/>
     </row>
     <row r="40" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="29"/>
@@ -2082,7 +2082,7 @@
         <v>10</v>
       </c>
       <c r="K40" s="17"/>
-      <c r="L40" s="40"/>
+      <c r="L40" s="27"/>
     </row>
     <row r="41" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="29"/>
@@ -2104,7 +2104,7 @@
         <v>10</v>
       </c>
       <c r="K41" s="17"/>
-      <c r="L41" s="40"/>
+      <c r="L41" s="27"/>
     </row>
     <row r="42" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="29"/>
@@ -2126,7 +2126,7 @@
         <v>10</v>
       </c>
       <c r="K42" s="17"/>
-      <c r="L42" s="40"/>
+      <c r="L42" s="27"/>
     </row>
     <row r="43" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="29"/>
@@ -2148,7 +2148,7 @@
         <v>10</v>
       </c>
       <c r="K43" s="17"/>
-      <c r="L43" s="40"/>
+      <c r="L43" s="27"/>
     </row>
     <row r="44" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29"/>
@@ -2170,12 +2170,12 @@
         <v>10</v>
       </c>
       <c r="K44" s="17"/>
-      <c r="L44" s="40"/>
+      <c r="L44" s="27"/>
     </row>
     <row r="45" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="29"/>
       <c r="B45" s="29"/>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="28" t="s">
         <v>83</v>
       </c>
       <c r="D45" s="32" t="s">
@@ -2200,7 +2200,7 @@
         <v>100000</v>
       </c>
       <c r="K45" s="17"/>
-      <c r="L45" s="40"/>
+      <c r="L45" s="27"/>
     </row>
     <row r="46" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="29"/>
@@ -2222,7 +2222,7 @@
         <v>100000</v>
       </c>
       <c r="K46" s="17"/>
-      <c r="L46" s="40"/>
+      <c r="L46" s="27"/>
     </row>
     <row r="47" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="29"/>
@@ -2244,7 +2244,7 @@
         <v>100000</v>
       </c>
       <c r="K47" s="17"/>
-      <c r="L47" s="40"/>
+      <c r="L47" s="27"/>
     </row>
     <row r="48" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29"/>
@@ -2266,7 +2266,7 @@
         <v>100000</v>
       </c>
       <c r="K48" s="17"/>
-      <c r="L48" s="40"/>
+      <c r="L48" s="27"/>
     </row>
     <row r="49" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="29"/>
@@ -2288,7 +2288,7 @@
         <v>100000</v>
       </c>
       <c r="K49" s="17"/>
-      <c r="L49" s="40"/>
+      <c r="L49" s="27"/>
     </row>
     <row r="50" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="29"/>
@@ -2310,12 +2310,12 @@
         <v>100000</v>
       </c>
       <c r="K50" s="17"/>
-      <c r="L50" s="40"/>
+      <c r="L50" s="27"/>
     </row>
     <row r="51" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="29"/>
       <c r="B51" s="29"/>
-      <c r="C51" s="28"/>
+      <c r="C51" s="30"/>
       <c r="D51" s="34"/>
       <c r="E51" s="16" t="s">
         <v>90</v>
@@ -2332,11 +2332,11 @@
         <v>100000</v>
       </c>
       <c r="K51" s="17"/>
-      <c r="L51" s="40"/>
+      <c r="L51" s="27"/>
     </row>
     <row r="52" spans="1:12" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="28"/>
-      <c r="B52" s="28"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
       <c r="C52" s="24" t="s">
         <v>99</v>
       </c>
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="K52" s="17"/>
-      <c r="L52" s="40"/>
+      <c r="L52" s="27"/>
     </row>
     <row r="53" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="35" t="s">
         <v>93</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -2396,11 +2396,11 @@
         <v>37</v>
       </c>
       <c r="K53" s="17"/>
-      <c r="L53" s="40"/>
+      <c r="L53" s="27"/>
     </row>
     <row r="54" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="29"/>
-      <c r="B54" s="30"/>
+      <c r="B54" s="36"/>
       <c r="C54" s="10" t="s">
         <v>96</v>
       </c>
@@ -2426,11 +2426,11 @@
         <v>37</v>
       </c>
       <c r="K54" s="17"/>
-      <c r="L54" s="39"/>
+      <c r="L54" s="26"/>
     </row>
     <row r="55" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="29"/>
-      <c r="B55" s="30"/>
+      <c r="B55" s="36"/>
       <c r="C55" s="10" t="s">
         <v>97</v>
       </c>
@@ -2456,11 +2456,11 @@
         <v>37</v>
       </c>
       <c r="K55" s="17"/>
-      <c r="L55" s="40"/>
+      <c r="L55" s="27"/>
     </row>
     <row r="56" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="28"/>
-      <c r="B56" s="26"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="37"/>
       <c r="C56" s="10" t="s">
         <v>94</v>
       </c>
@@ -2486,16 +2486,16 @@
         <v>37</v>
       </c>
       <c r="K56" s="17"/>
-      <c r="L56" s="40"/>
+      <c r="L56" s="27"/>
     </row>
     <row r="57" spans="1:12" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="C57" s="28" t="s">
         <v>46</v>
       </c>
       <c r="D57" s="10" t="s">
@@ -2520,12 +2520,12 @@
         <v>104</v>
       </c>
       <c r="K57" s="17"/>
-      <c r="L57" s="40"/>
+      <c r="L57" s="27"/>
     </row>
     <row r="58" spans="1:12" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="28"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="28"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="30"/>
       <c r="D58" s="23" t="s">
         <v>47</v>
       </c>
@@ -2548,10 +2548,20 @@
         <v>104</v>
       </c>
       <c r="K58" s="17"/>
-      <c r="L58" s="40"/>
+      <c r="L58" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="D10:D37"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="C10:C23"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A38:A52"/>
+    <mergeCell ref="B38:B52"/>
+    <mergeCell ref="C38:C44"/>
+    <mergeCell ref="C57:C58"/>
     <mergeCell ref="F10:F37"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="D38:D44"/>
@@ -2568,16 +2578,6 @@
     <mergeCell ref="I10:I37"/>
     <mergeCell ref="A10:A37"/>
     <mergeCell ref="B10:B37"/>
-    <mergeCell ref="D10:D37"/>
-    <mergeCell ref="B53:B56"/>
-    <mergeCell ref="A53:A56"/>
-    <mergeCell ref="C10:C23"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A38:A52"/>
-    <mergeCell ref="B38:B52"/>
-    <mergeCell ref="C38:C44"/>
-    <mergeCell ref="C57:C58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MeasureControl/加放油测试脚本V3.xlsx
+++ b/MeasureControl/加放油测试脚本V3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\application\C#\project\jiaoben\MeasureControl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\software\VisualStudio\Project\MC_jiaoben\MeasureControl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5862D612-4297-4A58-A438-8A35B03B5D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284E24EB-871F-4E94-88E4-E2BAFFCFC905}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="107">
   <si>
     <t>加放油控制器测试脚本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -432,6 +432,14 @@
   </si>
   <si>
     <t>0xAA55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>--</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>J6 对地阻抗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +498,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -515,6 +523,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -677,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -712,18 +726,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -760,6 +768,15 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -790,13 +807,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1088,7 +1105,7 @@
   <dimension ref="A1:N58"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="20.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23" style="2" customWidth="1"/>
     <col min="2" max="2" width="42.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="82.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="32.875" style="2" customWidth="1"/>
@@ -1102,20 +1119,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="69.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1156,13 +1173,13 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="29" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1186,13 +1203,13 @@
       <c r="J3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="23"/>
     </row>
     <row r="4" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
@@ -1214,13 +1231,13 @@
       <c r="J4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="25"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
@@ -1242,13 +1259,13 @@
       <c r="J5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="23"/>
     </row>
     <row r="6" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
+      <c r="A6" s="38"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
@@ -1270,8 +1287,8 @@
       <c r="J6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="25"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="23"/>
     </row>
     <row r="7" spans="1:14" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
@@ -1298,15 +1315,15 @@
       <c r="H7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="16">
         <v>18</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="20"/>
-      <c r="N7" s="13"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="18"/>
+      <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
@@ -1318,7 +1335,7 @@
       <c r="C8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -1339,8 +1356,8 @@
       <c r="J8" s="10">
         <v>15</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="20"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" spans="1:14" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -1367,32 +1384,32 @@
       <c r="H9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="16">
         <v>18</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="20"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>14</v>
+      <c r="D10" s="33" t="s">
+        <v>10</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="29" t="s">
         <v>75</v>
       </c>
       <c r="G10" s="7" t="s">
@@ -1401,628 +1418,628 @@
       <c r="H10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="38">
-        <v>18</v>
-      </c>
-      <c r="J10" s="18">
+      <c r="I10" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="26">
         <v>1</v>
       </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="27"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="15">
+      <c r="I11" s="40"/>
+      <c r="J11" s="27">
         <v>1</v>
       </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="27"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="29"/>
+      <c r="F12" s="30"/>
       <c r="G12" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="39"/>
-      <c r="J12" s="18">
+      <c r="I12" s="40"/>
+      <c r="J12" s="26">
         <v>1</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="27"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="29"/>
+      <c r="F13" s="30"/>
       <c r="G13" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="39"/>
-      <c r="J13" s="18">
+      <c r="I13" s="40"/>
+      <c r="J13" s="26">
         <v>1</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="27"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="29"/>
+      <c r="F14" s="30"/>
       <c r="G14" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="39"/>
-      <c r="J14" s="15">
+      <c r="I14" s="40"/>
+      <c r="J14" s="27">
         <v>1</v>
       </c>
-      <c r="K14" s="17"/>
-      <c r="L14" s="27"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="29"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="39"/>
-      <c r="J15" s="18">
+      <c r="I15" s="40"/>
+      <c r="J15" s="26">
         <v>1</v>
       </c>
-      <c r="K15" s="17"/>
-      <c r="L15" s="27"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:14" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="29"/>
+      <c r="F16" s="30"/>
       <c r="G16" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="18">
+      <c r="I16" s="40"/>
+      <c r="J16" s="26">
         <v>1</v>
       </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="27"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
       <c r="E17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="29"/>
+      <c r="F17" s="30"/>
       <c r="G17" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="39"/>
-      <c r="J17" s="15">
+      <c r="I17" s="40"/>
+      <c r="J17" s="27">
         <v>1</v>
       </c>
-      <c r="K17" s="17"/>
-      <c r="L17" s="27"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
       <c r="E18" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="29"/>
+      <c r="F18" s="30"/>
       <c r="G18" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="39"/>
-      <c r="J18" s="18">
+      <c r="I18" s="40"/>
+      <c r="J18" s="26">
         <v>1</v>
       </c>
-      <c r="K18" s="17"/>
-      <c r="L18" s="27"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
       <c r="E19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="29"/>
+      <c r="F19" s="30"/>
       <c r="G19" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I19" s="39"/>
-      <c r="J19" s="18">
+      <c r="I19" s="40"/>
+      <c r="J19" s="26">
         <v>1</v>
       </c>
-      <c r="K19" s="17"/>
-      <c r="L19" s="27"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
       <c r="E20" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="29"/>
+      <c r="F20" s="30"/>
       <c r="G20" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="18">
+      <c r="I20" s="40"/>
+      <c r="J20" s="26">
         <v>1</v>
       </c>
-      <c r="K20" s="17"/>
-      <c r="L20" s="27"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="29"/>
+      <c r="F21" s="30"/>
       <c r="G21" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I21" s="39"/>
-      <c r="J21" s="18">
+      <c r="I21" s="40"/>
+      <c r="J21" s="26">
         <v>1</v>
       </c>
-      <c r="K21" s="17"/>
-      <c r="L21" s="27"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="29"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="18">
+      <c r="I22" s="40"/>
+      <c r="J22" s="26">
         <v>1</v>
       </c>
-      <c r="K22" s="17"/>
-      <c r="L22" s="27"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="29"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="30"/>
       <c r="E23" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="29"/>
+      <c r="F23" s="30"/>
       <c r="G23" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="18">
+      <c r="I23" s="40"/>
+      <c r="J23" s="26">
         <v>1</v>
       </c>
-      <c r="K23" s="17"/>
-      <c r="L23" s="27"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="28" t="s">
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="29"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="29"/>
+      <c r="F24" s="30"/>
       <c r="G24" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="18">
+      <c r="I24" s="40"/>
+      <c r="J24" s="26">
         <v>0</v>
       </c>
-      <c r="K24" s="17"/>
-      <c r="L24" s="27"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="25"/>
     </row>
     <row r="25" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="29"/>
+      <c r="F25" s="30"/>
       <c r="G25" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="18">
+      <c r="I25" s="40"/>
+      <c r="J25" s="26">
         <v>0</v>
       </c>
-      <c r="K25" s="17"/>
-      <c r="L25" s="27"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="29"/>
+      <c r="F26" s="30"/>
       <c r="G26" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="18">
+      <c r="I26" s="40"/>
+      <c r="J26" s="26">
         <v>0</v>
       </c>
-      <c r="K26" s="17"/>
-      <c r="L26" s="27"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="25"/>
     </row>
     <row r="27" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="29"/>
+      <c r="F27" s="30"/>
       <c r="G27" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I27" s="39"/>
-      <c r="J27" s="18">
+      <c r="I27" s="40"/>
+      <c r="J27" s="26">
         <v>0</v>
       </c>
-      <c r="K27" s="17"/>
-      <c r="L27" s="27"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F28" s="29"/>
+      <c r="F28" s="30"/>
       <c r="G28" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I28" s="39"/>
-      <c r="J28" s="12">
+      <c r="I28" s="40"/>
+      <c r="J28" s="28">
         <v>0</v>
       </c>
-      <c r="K28" s="17"/>
-      <c r="L28" s="27"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="29"/>
+      <c r="F29" s="30"/>
       <c r="G29" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I29" s="39"/>
-      <c r="J29" s="18">
+      <c r="I29" s="40"/>
+      <c r="J29" s="26">
         <v>0</v>
       </c>
-      <c r="K29" s="17"/>
-      <c r="L29" s="27"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="29"/>
+      <c r="F30" s="30"/>
       <c r="G30" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I30" s="39"/>
-      <c r="J30" s="18">
+      <c r="I30" s="40"/>
+      <c r="J30" s="26">
         <v>0</v>
       </c>
-      <c r="K30" s="17"/>
-      <c r="L30" s="27"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="29"/>
+      <c r="F31" s="30"/>
       <c r="G31" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I31" s="39"/>
-      <c r="J31" s="18">
+      <c r="I31" s="40"/>
+      <c r="J31" s="26">
         <v>0</v>
       </c>
-      <c r="K31" s="17"/>
-      <c r="L31" s="27"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="29"/>
+      <c r="F32" s="30"/>
       <c r="G32" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I32" s="39"/>
-      <c r="J32" s="18">
+      <c r="I32" s="40"/>
+      <c r="J32" s="26">
         <v>0</v>
       </c>
-      <c r="K32" s="17"/>
-      <c r="L32" s="27"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="29"/>
+      <c r="F33" s="30"/>
       <c r="G33" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I33" s="39"/>
-      <c r="J33" s="18">
+      <c r="I33" s="40"/>
+      <c r="J33" s="26">
         <v>0</v>
       </c>
-      <c r="K33" s="17"/>
-      <c r="L33" s="27"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="29"/>
+      <c r="F34" s="30"/>
       <c r="G34" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I34" s="39"/>
-      <c r="J34" s="18">
+      <c r="I34" s="40"/>
+      <c r="J34" s="26">
         <v>0</v>
       </c>
-      <c r="K34" s="17"/>
-      <c r="L34" s="27"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="29"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F35" s="29"/>
+      <c r="F35" s="30"/>
       <c r="G35" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="39"/>
-      <c r="J35" s="18">
+      <c r="I35" s="40"/>
+      <c r="J35" s="26">
         <v>0</v>
       </c>
-      <c r="K35" s="17"/>
-      <c r="L35" s="27"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="29"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F36" s="29"/>
+      <c r="F36" s="30"/>
       <c r="G36" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I36" s="39"/>
-      <c r="J36" s="18">
+      <c r="I36" s="40"/>
+      <c r="J36" s="26">
         <v>0</v>
       </c>
-      <c r="K36" s="17"/>
-      <c r="L36" s="27"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
+      <c r="A37" s="31"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
       <c r="E37" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="30"/>
+      <c r="F37" s="31"/>
       <c r="G37" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="40"/>
-      <c r="J37" s="18">
+      <c r="I37" s="41"/>
+      <c r="J37" s="26">
         <v>0</v>
       </c>
-      <c r="K37" s="17"/>
-      <c r="L37" s="27"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" s="32" t="s">
+      <c r="E38" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="33" t="s">
         <v>101</v>
       </c>
       <c r="G38" s="7" t="s">
@@ -2031,160 +2048,160 @@
       <c r="H38" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I38" s="32" t="s">
+      <c r="I38" s="33" t="s">
         <v>101</v>
       </c>
       <c r="J38" s="10">
         <v>10</v>
       </c>
-      <c r="K38" s="17"/>
-      <c r="L38" s="27"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="25"/>
     </row>
     <row r="39" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="29"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="16" t="s">
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F39" s="33"/>
+      <c r="F39" s="34"/>
       <c r="G39" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I39" s="33"/>
+      <c r="I39" s="34"/>
       <c r="J39" s="10">
         <v>10</v>
       </c>
-      <c r="K39" s="17"/>
-      <c r="L39" s="27"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="25"/>
     </row>
     <row r="40" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="16" t="s">
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F40" s="33"/>
+      <c r="F40" s="34"/>
       <c r="G40" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I40" s="33"/>
+      <c r="I40" s="34"/>
       <c r="J40" s="10">
         <v>10</v>
       </c>
-      <c r="K40" s="17"/>
-      <c r="L40" s="27"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="25"/>
     </row>
     <row r="41" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="29"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="16" t="s">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="F41" s="33"/>
+      <c r="F41" s="34"/>
       <c r="G41" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I41" s="33"/>
+      <c r="I41" s="34"/>
       <c r="J41" s="10">
         <v>10</v>
       </c>
-      <c r="K41" s="17"/>
-      <c r="L41" s="27"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="25"/>
     </row>
     <row r="42" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="29"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="16" t="s">
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F42" s="33"/>
+      <c r="F42" s="34"/>
       <c r="G42" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I42" s="33"/>
+      <c r="I42" s="34"/>
       <c r="J42" s="10">
         <v>10</v>
       </c>
-      <c r="K42" s="17"/>
-      <c r="L42" s="27"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="25"/>
     </row>
     <row r="43" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="16" t="s">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F43" s="33"/>
+      <c r="F43" s="34"/>
       <c r="G43" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I43" s="33"/>
+      <c r="I43" s="34"/>
       <c r="J43" s="10">
         <v>10</v>
       </c>
-      <c r="K43" s="17"/>
-      <c r="L43" s="27"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="25"/>
     </row>
     <row r="44" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="16" t="s">
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F44" s="34"/>
+      <c r="F44" s="35"/>
       <c r="G44" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I44" s="34"/>
+      <c r="I44" s="35"/>
       <c r="J44" s="10">
         <v>10</v>
       </c>
-      <c r="K44" s="17"/>
-      <c r="L44" s="27"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="25"/>
     </row>
     <row r="45" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="28" t="s">
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F45" s="32" t="s">
+      <c r="F45" s="33" t="s">
         <v>101</v>
       </c>
       <c r="G45" s="7" t="s">
@@ -2193,157 +2210,157 @@
       <c r="H45" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I45" s="32" t="s">
+      <c r="I45" s="33" t="s">
         <v>101</v>
       </c>
       <c r="J45" s="10">
         <v>100000</v>
       </c>
-      <c r="K45" s="17"/>
-      <c r="L45" s="27"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="25"/>
     </row>
     <row r="46" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="16" t="s">
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F46" s="33"/>
+      <c r="F46" s="34"/>
       <c r="G46" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I46" s="33"/>
+      <c r="I46" s="34"/>
       <c r="J46" s="10">
         <v>100000</v>
       </c>
-      <c r="K46" s="17"/>
-      <c r="L46" s="27"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="25"/>
     </row>
     <row r="47" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="16" t="s">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="33"/>
+      <c r="F47" s="34"/>
       <c r="G47" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I47" s="33"/>
+      <c r="I47" s="34"/>
       <c r="J47" s="10">
         <v>100000</v>
       </c>
-      <c r="K47" s="17"/>
-      <c r="L47" s="27"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="25"/>
     </row>
     <row r="48" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="29"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="16" t="s">
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="F48" s="33"/>
+      <c r="F48" s="34"/>
       <c r="G48" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I48" s="33"/>
+      <c r="I48" s="34"/>
       <c r="J48" s="10">
         <v>100000</v>
       </c>
-      <c r="K48" s="17"/>
-      <c r="L48" s="27"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="25"/>
     </row>
     <row r="49" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="16" t="s">
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F49" s="33"/>
+      <c r="F49" s="34"/>
       <c r="G49" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I49" s="33"/>
+      <c r="I49" s="34"/>
       <c r="J49" s="10">
         <v>100000</v>
       </c>
-      <c r="K49" s="17"/>
-      <c r="L49" s="27"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="25"/>
     </row>
     <row r="50" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="16" t="s">
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F50" s="33"/>
+      <c r="F50" s="34"/>
       <c r="G50" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I50" s="33"/>
+      <c r="I50" s="34"/>
       <c r="J50" s="10">
         <v>100000</v>
       </c>
-      <c r="K50" s="17"/>
-      <c r="L50" s="27"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="25"/>
     </row>
     <row r="51" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="16" t="s">
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F51" s="34"/>
+      <c r="F51" s="35"/>
       <c r="G51" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H51" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I51" s="34"/>
+      <c r="I51" s="35"/>
       <c r="J51" s="10">
         <v>100000</v>
       </c>
-      <c r="K51" s="17"/>
-      <c r="L51" s="27"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="25"/>
     </row>
     <row r="52" spans="1:12" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="30"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="24" t="s">
+      <c r="A52" s="31"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="D52" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E52" s="14" t="s">
         <v>30</v>
       </c>
       <c r="F52" s="10" t="s">
@@ -2355,20 +2372,20 @@
       <c r="H52" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I52" s="18">
+      <c r="I52" s="16">
         <v>18</v>
       </c>
-      <c r="J52" s="18">
+      <c r="J52" s="16">
         <v>16</v>
       </c>
-      <c r="K52" s="17"/>
-      <c r="L52" s="27"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="25"/>
     </row>
     <row r="53" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="28" t="s">
+      <c r="A53" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B53" s="35" t="s">
+      <c r="B53" s="36" t="s">
         <v>93</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -2392,15 +2409,15 @@
       <c r="I53" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J53" s="18" t="s">
+      <c r="J53" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K53" s="17"/>
-      <c r="L53" s="27"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="25"/>
     </row>
     <row r="54" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="29"/>
-      <c r="B54" s="36"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="37"/>
       <c r="C54" s="10" t="s">
         <v>96</v>
       </c>
@@ -2422,15 +2439,15 @@
       <c r="I54" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J54" s="18" t="s">
+      <c r="J54" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K54" s="17"/>
-      <c r="L54" s="26"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="24"/>
     </row>
     <row r="55" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="29"/>
-      <c r="B55" s="36"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="37"/>
       <c r="C55" s="10" t="s">
         <v>97</v>
       </c>
@@ -2452,15 +2469,15 @@
       <c r="I55" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J55" s="18" t="s">
+      <c r="J55" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K55" s="17"/>
-      <c r="L55" s="27"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="25"/>
     </row>
     <row r="56" spans="1:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="30"/>
-      <c r="B56" s="37"/>
+      <c r="A56" s="31"/>
+      <c r="B56" s="38"/>
       <c r="C56" s="10" t="s">
         <v>94</v>
       </c>
@@ -2482,20 +2499,20 @@
       <c r="I56" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J56" s="18" t="s">
+      <c r="J56" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K56" s="17"/>
-      <c r="L56" s="27"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="25"/>
     </row>
     <row r="57" spans="1:12" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B57" s="35" t="s">
+      <c r="B57" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D57" s="10" t="s">
@@ -2519,14 +2536,14 @@
       <c r="J57" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="K57" s="17"/>
-      <c r="L57" s="27"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="25"/>
     </row>
     <row r="58" spans="1:12" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="30"/>
-      <c r="B58" s="37"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="23" t="s">
+      <c r="A58" s="31"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="21" t="s">
         <v>47</v>
       </c>
       <c r="E58" s="6" t="s">
@@ -2547,8 +2564,8 @@
       <c r="J58" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="K58" s="17"/>
-      <c r="L58" s="27"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -2581,5 +2598,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>
 </file>